--- a/exports/BHARTIARTL_full_report.xlsx
+++ b/exports/BHARTIARTL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>3.54</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>713.85</v>
+        <v>702.2</v>
       </c>
       <c r="I2" t="n">
         <v>703.44705990395</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="L2" t="n">
         <v>1.77</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>5.28</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44589.55208333334</v>
+        <v>44592.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>717</v>
+        <v>730.95</v>
       </c>
       <c r="I3" t="n">
         <v>725.0089629084019</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.11</v>
+        <v>-4.09</v>
       </c>
       <c r="L3" t="n">
         <v>7.11</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="N3" t="n">
         <v>3.16</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.43</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>701.2</v>
+        <v>680.6</v>
       </c>
       <c r="I4" t="n">
         <v>687.4641958707243</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.07</v>
+        <v>-6.89</v>
       </c>
       <c r="L4" t="n">
-        <v>6.29</v>
+        <v>11.64</v>
       </c>
       <c r="M4" t="n">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="N4" t="n">
-        <v>3.39</v>
+        <v>4.46</v>
       </c>
       <c r="O4" t="n">
         <v>1.75</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>5.3</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44631.55208333334</v>
+        <v>44634.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>694.4</v>
+        <v>702.85</v>
       </c>
       <c r="I5" t="n">
         <v>699.107070422624</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.03</v>
+        <v>-3.27</v>
       </c>
       <c r="L5" t="n">
         <v>3.94</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.98</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>739.9</v>
+        <v>724.95</v>
       </c>
       <c r="I6" t="n">
         <v>738.5035050809847</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>5.27</v>
+        <v>3.14</v>
       </c>
       <c r="L6" t="n">
         <v>2.09</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.72</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>671</v>
+        <v>679.1</v>
       </c>
       <c r="I7" t="n">
         <v>676.4262456490075</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K7" t="n">
-        <v>7.44</v>
+        <v>6.32</v>
       </c>
       <c r="L7" t="n">
         <v>5.04</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>5.58</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>693.45</v>
+        <v>662.2</v>
       </c>
       <c r="I8" t="n">
         <v>669.83215586095</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>2.11</v>
+        <v>-2.49</v>
       </c>
       <c r="L8" t="n">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="N8" t="n">
-        <v>1.74</v>
+        <v>4.88</v>
       </c>
       <c r="O8" t="n">
         <v>2.28</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.17</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44763.38541666666</v>
+        <v>44763.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>675.3</v>
+        <v>677.2</v>
       </c>
       <c r="I9" t="n">
         <v>675.7217801571007</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.98</v>
+        <v>-2.27</v>
       </c>
       <c r="L9" t="n">
         <v>2.82</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.33</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>762.65</v>
+        <v>755</v>
       </c>
       <c r="I10" t="n">
         <v>762.2471093436926</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>66.83333333333333</v>
+        <v>67</v>
       </c>
       <c r="K10" t="n">
-        <v>12.62</v>
+        <v>11.49</v>
       </c>
       <c r="L10" t="n">
         <v>1.89</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>4.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44834.38541666666</v>
+        <v>44834.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>784</v>
+        <v>799.6</v>
       </c>
       <c r="I11" t="n">
         <v>790.1188882210058</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.84</v>
+        <v>-5.91</v>
       </c>
       <c r="L11" t="n">
-        <v>4.06</v>
+        <v>7.15</v>
       </c>
       <c r="M11" t="n">
         <v>0.59</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.26</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44846.55208333334</v>
+        <v>44847.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>776.9</v>
+        <v>770</v>
       </c>
       <c r="I12" t="n">
         <v>771.8513486553009</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.84</v>
+        <v>-3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>4.87</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44854.55208333334</v>
+        <v>44855.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>791</v>
+        <v>799.55</v>
       </c>
       <c r="I13" t="n">
         <v>796.8611316815102</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.73</v>
+        <v>-3.84</v>
       </c>
       <c r="L13" t="n">
-        <v>3.09</v>
+        <v>4.26</v>
       </c>
       <c r="M13" t="n">
         <v>1.42</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.08</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>825.85</v>
+        <v>822.9</v>
       </c>
       <c r="I14" t="n">
         <v>824.0504034623548</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="L14" t="n">
         <v>1.23</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>3.07</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>764.4</v>
+        <v>773.95</v>
       </c>
       <c r="I15" t="n">
         <v>768.7058751173062</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>77</v>
+        <v>79.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>7.11</v>
+        <v>5.95</v>
       </c>
       <c r="L15" t="n">
         <v>2.59</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.53</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45013.55208333334</v>
+        <v>45014.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>748</v>
+        <v>740.55</v>
       </c>
       <c r="I16" t="n">
         <v>747.0861927396054</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.35</v>
+        <v>-4.32</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="M16" t="n">
         <v>1.64</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.05</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45022.55208333334</v>
+        <v>45026.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>765.1</v>
+        <v>774.1</v>
       </c>
       <c r="I17" t="n">
         <v>772.1154098594751</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.32</v>
+        <v>-4.53</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8</v>
+        <v>4.81</v>
       </c>
       <c r="M17" t="n">
         <v>0.96</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.76</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>870.3</v>
+        <v>861.6</v>
       </c>
       <c r="I18" t="n">
         <v>865.739571376477</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>123.1666666666667</v>
+        <v>126</v>
       </c>
       <c r="K18" t="n">
-        <v>12.43</v>
+        <v>11.3</v>
       </c>
       <c r="L18" t="n">
         <v>2.78</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>3.92</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45176.55208333334</v>
+        <v>45177.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>876</v>
+        <v>886.9</v>
       </c>
       <c r="I19" t="n">
         <v>880.4373732902731</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.67</v>
+        <v>-2.94</v>
       </c>
       <c r="L19" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="M19" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="N19" t="n">
         <v>1.87</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>3.3</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>940.45</v>
+        <v>919.4</v>
       </c>
       <c r="I20" t="n">
         <v>928.9881508974196</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K20" t="n">
-        <v>6.04</v>
+        <v>3.66</v>
       </c>
       <c r="L20" t="n">
         <v>0.99</v>
       </c>
       <c r="M20" t="n">
-        <v>1.21</v>
+        <v>1.69</v>
       </c>
       <c r="N20" t="n">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
         <v>0.85</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>934.25</v>
+        <v>944.2</v>
       </c>
       <c r="I21" t="n">
         <v>938.6962902166963</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.62</v>
+        <v>-2.7</v>
       </c>
       <c r="L21" t="n">
-        <v>2.44</v>
+        <v>3.11</v>
       </c>
       <c r="M21" t="n">
-        <v>0.77</v>
+        <v>1.47</v>
       </c>
       <c r="N21" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="O21" t="n">
         <v>-1.7</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>2.51</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45267.55208333334</v>
+        <v>45268.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>999.95</v>
+        <v>993.65</v>
       </c>
       <c r="I22" t="n">
         <v>998.4967243021808</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K22" t="n">
-        <v>5.9</v>
+        <v>5.24</v>
       </c>
       <c r="L22" t="n">
         <v>0.85</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.2</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45286.55208333334</v>
+        <v>45287.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1000</v>
+        <v>1018.45</v>
       </c>
       <c r="I23" t="n">
         <v>1006.648512239625</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.64</v>
+        <v>-2.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.77</v>
+        <v>3.06</v>
       </c>
       <c r="M23" t="n">
         <v>0.75</v>
       </c>
       <c r="N23" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
         <v>0.21</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.7</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45324.55208333334</v>
+        <v>45327.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1152.8</v>
+        <v>1119.15</v>
       </c>
       <c r="I24" t="n">
         <v>1121.470069840905</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K24" t="n">
-        <v>13.19</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>2.01</v>
@@ -1809,7 +2096,7 @@
         <v>1.63</v>
       </c>
       <c r="N24" t="n">
-        <v>2.31</v>
+        <v>3.32</v>
       </c>
       <c r="O24" t="n">
         <v>2</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.03</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45355.55208333334</v>
+        <v>45356.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1133.25</v>
+        <v>1161.75</v>
       </c>
       <c r="I25" t="n">
         <v>1161.143391322084</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.26</v>
+        <v>-3.81</v>
       </c>
       <c r="L25" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
         <v>0.99</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
         <v>-3.32</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.11</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45414.55208333334</v>
+        <v>45415.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1304</v>
+        <v>1263.8</v>
       </c>
       <c r="I26" t="n">
         <v>1280.058061225549</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K26" t="n">
-        <v>12.24</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>2.47</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>6.91</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45427.55208333334</v>
+        <v>45428.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1316.05</v>
+        <v>1335.2</v>
       </c>
       <c r="I27" t="n">
         <v>1334.483848936738</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.13</v>
+        <v>-5.65</v>
       </c>
       <c r="L27" t="n">
-        <v>4.31</v>
+        <v>7.36</v>
       </c>
       <c r="M27" t="n">
-        <v>0.28</v>
+        <v>0.91</v>
       </c>
       <c r="N27" t="n">
         <v>2.25</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>4.77</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1400</v>
+        <v>1271.65</v>
       </c>
       <c r="I28" t="n">
         <v>1337.251923282263</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>4.85</v>
+        <v>-4.76</v>
       </c>
       <c r="L28" t="n">
-        <v>1.04</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>0.92</v>
       </c>
       <c r="N28" t="n">
-        <v>0.9</v>
+        <v>7.72</v>
       </c>
       <c r="O28" t="n">
         <v>2.12</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.7</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45454.55208333334</v>
+        <v>45455.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1424.6</v>
+        <v>1445.55</v>
       </c>
       <c r="I29" t="n">
         <v>1430.983880034147</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>-12.03</v>
+        <v>-13.68</v>
       </c>
       <c r="L29" t="n">
-        <v>12.98</v>
+        <v>13.86</v>
       </c>
       <c r="M29" t="n">
         <v>2.61</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.24</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45509.55208333334</v>
+        <v>45510.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1466.5</v>
+        <v>1436.4</v>
       </c>
       <c r="I30" t="n">
         <v>1440.649661995121</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K30" t="n">
-        <v>1.45</v>
+        <v>-0.63</v>
       </c>
       <c r="L30" t="n">
         <v>5.03</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>7.15</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45527.55208333334</v>
+        <v>45530.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1509.5</v>
+        <v>1513.8</v>
       </c>
       <c r="I31" t="n">
         <v>1509.908284793518</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.09</v>
+        <v>-5.39</v>
       </c>
       <c r="L31" t="n">
-        <v>5.12</v>
+        <v>5.87</v>
       </c>
       <c r="M31" t="n">
         <v>1.13</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>3.75</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1705</v>
+        <v>1686.8</v>
       </c>
       <c r="I32" t="n">
         <v>1691.98332376277</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K32" t="n">
-        <v>12.63</v>
+        <v>11.43</v>
       </c>
       <c r="L32" t="n">
         <v>0.78</v>
       </c>
       <c r="M32" t="n">
-        <v>1.32</v>
+        <v>2.35</v>
       </c>
       <c r="N32" t="n">
         <v>1.71</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>3.99</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45579.55208333334</v>
+        <v>45580.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1691.8</v>
+        <v>1722.45</v>
       </c>
       <c r="I33" t="n">
         <v>1714.217382041448</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.3</v>
+        <v>-2.11</v>
       </c>
       <c r="L33" t="n">
-        <v>1.38</v>
+        <v>2.72</v>
       </c>
       <c r="M33" t="n">
-        <v>0.43</v>
+        <v>0.96</v>
       </c>
       <c r="N33" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="O33" t="n">
         <v>-1.2</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>4.7</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45589.55208333334</v>
+        <v>45590.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1682.95</v>
+        <v>1667.05</v>
       </c>
       <c r="I34" t="n">
         <v>1669.338602809783</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.29</v>
+        <v>-3.22</v>
       </c>
       <c r="L34" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="M34" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="N34" t="n">
         <v>1.73</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>4.33</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45624.55208333334</v>
+        <v>45625.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1564.95</v>
+        <v>1642.9</v>
       </c>
       <c r="I35" t="n">
         <v>1593.057599786313</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>6.12</v>
+        <v>1.45</v>
       </c>
       <c r="L35" t="n">
         <v>1.06</v>
@@ -2436,7 +2855,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>2.91</v>
+        <v>4.09</v>
       </c>
       <c r="O35" t="n">
         <v>-0.72</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.52</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1599</v>
+        <v>1584.7</v>
       </c>
       <c r="I36" t="n">
         <v>1597.142012730715</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.67</v>
+        <v>-3.54</v>
       </c>
       <c r="L36" t="n">
         <v>5.58</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>5.68</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45677.55208333334</v>
+        <v>45678.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1640</v>
+        <v>1651.6</v>
       </c>
       <c r="I37" t="n">
         <v>1642.810881381121</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.49</v>
+        <v>-4.22</v>
       </c>
       <c r="L37" t="n">
-        <v>3.81</v>
+        <v>4.54</v>
       </c>
       <c r="M37" t="n">
         <v>0.88</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.63</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45706.55208333334</v>
+        <v>45707.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1669.5</v>
+        <v>1643.3</v>
       </c>
       <c r="I38" t="n">
         <v>1652.440299636535</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K38" t="n">
-        <v>1.08</v>
+        <v>-0.5</v>
       </c>
       <c r="L38" t="n">
         <v>4.68</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.15</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45726.55208333334</v>
+        <v>45727.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1628</v>
+        <v>1661.55</v>
       </c>
       <c r="I39" t="n">
         <v>1646.523957476571</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>0.93</v>
+        <v>-1.11</v>
       </c>
       <c r="L39" t="n">
         <v>1.83</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45790.38541666666</v>
+        <v>45790.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>1827.7</v>
+        <v>1822.2</v>
       </c>
       <c r="I40" t="n">
         <v>1824.397179156762</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K40" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="L40" t="n">
         <v>2.97</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>4.47</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45811.55208333334</v>
+        <v>45812.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1841.6</v>
+        <v>1880.4</v>
       </c>
       <c r="I41" t="n">
         <v>1874.810220757375</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.06</v>
+        <v>-3.19</v>
       </c>
       <c r="L41" t="n">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="M41" t="n">
         <v>0.92</v>
       </c>
       <c r="N41" t="n">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="O41" t="n">
         <v>-2.71</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>4.17</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45847.55208333334</v>
+        <v>45848.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2019.2</v>
+        <v>1973.6</v>
       </c>
       <c r="I42" t="n">
         <v>1974.811592538657</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K42" t="n">
-        <v>7.38</v>
+        <v>4.96</v>
       </c>
       <c r="L42" t="n">
         <v>3.48</v>
@@ -2835,7 +3338,7 @@
         <v>1.57</v>
       </c>
       <c r="N42" t="n">
-        <v>0.73</v>
+        <v>2.73</v>
       </c>
       <c r="O42" t="n">
         <v>1.71</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>5.04</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1912.9</v>
+        <v>1931.8</v>
       </c>
       <c r="I43" t="n">
         <v>1914.064496730083</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K43" t="n">
-        <v>3.08</v>
+        <v>2.12</v>
       </c>
       <c r="L43" t="n">
         <v>2.79</v>
       </c>
       <c r="M43" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="N43" t="n">
         <v>2.23</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>3.25</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45929.38541666666</v>
+        <v>45929.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1918</v>
+        <v>1903</v>
       </c>
       <c r="I44" t="n">
         <v>1904.059903007087</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.71</v>
+        <v>-1.49</v>
       </c>
       <c r="L44" t="n">
         <v>3.2</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>3.34</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45936.55208333334</v>
+        <v>45937.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1901.9</v>
+        <v>1938.5</v>
       </c>
       <c r="I45" t="n">
         <v>1923.741789196392</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>0.06</v>
+        <v>-1.87</v>
       </c>
       <c r="L45" t="n">
-        <v>0.97</v>
+        <v>1.94</v>
       </c>
       <c r="M45" t="n">
         <v>0.03</v>
       </c>
       <c r="N45" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="O45" t="n">
         <v>-0.65</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>4.29</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45967.55208333334</v>
+        <v>45968.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2095</v>
+        <v>2010.8</v>
       </c>
       <c r="I46" t="n">
         <v>2038.452961276604</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K46" t="n">
-        <v>8.07</v>
+        <v>3.73</v>
       </c>
       <c r="L46" t="n">
         <v>1.99</v>
       </c>
       <c r="M46" t="n">
-        <v>1.43</v>
+        <v>2.24</v>
       </c>
       <c r="N46" t="n">
-        <v>1.67</v>
+        <v>4.44</v>
       </c>
       <c r="O46" t="n">
         <v>1.64</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.72</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45975.55208333334</v>
+        <v>45978.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2097.9</v>
+        <v>2113.7</v>
       </c>
       <c r="I47" t="n">
         <v>2101.371329895778</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.33</v>
+        <v>-5.12</v>
       </c>
       <c r="L47" t="n">
-        <v>4.83</v>
+        <v>5.53</v>
       </c>
       <c r="M47" t="n">
         <v>1.06</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>3.53</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>2118</v>
+        <v>2105.8</v>
       </c>
       <c r="I48" t="n">
         <v>2107.010111151665</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2</v>
+        <v>-0.37</v>
       </c>
       <c r="L48" t="n">
         <v>0.77</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>3.88</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>2090.9</v>
+        <v>2147.7</v>
       </c>
       <c r="I49" t="n">
         <v>2111.655844657762</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>0.71</v>
+        <v>-1.99</v>
       </c>
       <c r="L49" t="n">
-        <v>1.13</v>
+        <v>2.15</v>
       </c>
       <c r="M49" t="n">
-        <v>0.74</v>
+        <v>1.3</v>
       </c>
       <c r="N49" t="n">
-        <v>1.59</v>
+        <v>2.39</v>
       </c>
       <c r="O49" t="n">
         <v>-0.85</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>4.5</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>2084</v>
+        <v>2062.3</v>
       </c>
       <c r="I50" t="n">
         <v>2072.644002794321</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.97</v>
+        <v>-3.98</v>
       </c>
       <c r="L50" t="n">
-        <v>3.54</v>
+        <v>4.32</v>
       </c>
       <c r="M50" t="n">
         <v>0.64</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>3.69</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46058.55208333334</v>
+        <v>46059.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1992.2</v>
+        <v>2029</v>
       </c>
       <c r="I51" t="n">
         <v>2026.2574467247</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K51" t="n">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="L51" t="n">
         <v>1.44</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.53</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46076.55208333334</v>
+        <v>46077.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1997</v>
+        <v>1945.1</v>
       </c>
       <c r="I52" t="n">
         <v>1959.733472264852</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.58</v>
+        <v>-4.14</v>
       </c>
       <c r="L52" t="n">
-        <v>2.86</v>
+        <v>5.28</v>
       </c>
       <c r="M52" t="n">
         <v>0.2</v>
       </c>
       <c r="N52" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="O52" t="n">
         <v>1.55</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.77</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46120.38541666666</v>
+        <v>46120.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1857.6</v>
+        <v>1861</v>
       </c>
       <c r="I53" t="n">
         <v>1859.140660678422</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K53" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="L53" t="n">
         <v>2.68</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>5.49</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46147.38541666666</v>
+        <v>46147.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1821</v>
+        <v>1816</v>
       </c>
       <c r="I54" t="n">
         <v>1818.296126858323</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.15</v>
+        <v>-2.42</v>
       </c>
       <c r="L54" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="M54" t="n">
         <v>1.58</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.4</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46155.55208333334</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1781.2</v>
+        <v>1873.8</v>
       </c>
       <c r="I55" t="n">
         <v>1837.035575497389</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>1.92</v>
+        <v>-3.18</v>
       </c>
       <c r="L55" t="n">
-        <v>1.54</v>
+        <v>3.35</v>
       </c>
       <c r="M55" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="N55" t="n">
-        <v>1.04</v>
+        <v>5.72</v>
       </c>
       <c r="O55" t="n">
         <v>-0.66</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.43</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46169.55208333334</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1847.4</v>
+        <v>1830.4</v>
       </c>
       <c r="I56" t="n">
         <v>1845.010976145895</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.41</v>
+        <v>-2.32</v>
       </c>
       <c r="L56" t="n">
         <v>4.08</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>4.53</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46190.38541666666</v>
+        <v>46190.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>1855</v>
+        <v>1874.2</v>
       </c>
       <c r="I57" t="n">
         <v>1856.16325900422</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.34</v>
+        <v>-2.39</v>
       </c>
       <c r="L57" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="M57" t="n">
         <v>0.93</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>4.03</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46198.38541666666</v>
+        <v>46198.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>1863.4</v>
+        <v>1849.9</v>
       </c>
       <c r="I58" t="n">
         <v>1853.833890940734</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.58</v>
+        <v>-1.3</v>
       </c>
       <c r="L58" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="M58" t="n">
         <v>0.44</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.07</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1871.2</v>
+        <v>1903.6</v>
       </c>
       <c r="I59" t="n">
         <v>1903.217479551298</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.15</v>
+        <v>-2.9</v>
       </c>
       <c r="L59" t="n">
-        <v>2.01</v>
+        <v>3.15</v>
       </c>
       <c r="M59" t="n">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>0.77</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
         <v>-1.31</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>4.18</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46226.55208333334</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1933</v>
+        <v>1891</v>
       </c>
       <c r="I60" t="n">
         <v>1893.565626113023</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K60" t="n">
-        <v>1.54</v>
+        <v>-0.66</v>
       </c>
       <c r="L60" t="n">
         <v>1.5</v>
       </c>
       <c r="M60" t="n">
-        <v>0.98</v>
+        <v>1.7</v>
       </c>
       <c r="N60" t="n">
         <v>1.93</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>3.43</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1946.6</v>
+        <v>1972.3</v>
       </c>
       <c r="I61" t="n">
         <v>1955.909558563606</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.94</v>
+        <v>-4.3</v>
       </c>
       <c r="L61" t="n">
-        <v>3.82</v>
+        <v>4.52</v>
       </c>
       <c r="M61" t="n">
-        <v>0.55</v>
+        <v>1.15</v>
       </c>
       <c r="N61" t="n">
         <v>2.17</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>3.78</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1919.6</v>
+        <v>1904.1</v>
       </c>
       <c r="I62" t="n">
         <v>1912.28858743579</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.67</v>
+        <v>-3.46</v>
       </c>
       <c r="L62" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="M62" t="n">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
       <c r="N62" t="n">
         <v>0.9399999999999999</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>3.43</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46247.55208333334</v>
+        <v>46248.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1938</v>
+        <v>1997.1</v>
       </c>
       <c r="I63" t="n">
         <v>1969.378476804276</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.78</v>
+        <v>-4.88</v>
       </c>
       <c r="L63" t="n">
-        <v>3.46</v>
+        <v>5.2</v>
       </c>
       <c r="M63" t="n">
         <v>2.45</v>
       </c>
       <c r="N63" t="n">
-        <v>1.04</v>
+        <v>2.79</v>
       </c>
       <c r="O63" t="n">
         <v>-0.08</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.75</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1943.8</v>
+        <v>1913.3</v>
       </c>
       <c r="I64" t="n">
         <v>1915.301496731843</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.67</v>
+        <v>-4.2</v>
       </c>
       <c r="L64" t="n">
-        <v>3.7</v>
+        <v>4.21</v>
       </c>
       <c r="M64" t="n">
         <v>0.95</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>3.76</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1770</v>
+        <v>1793.6</v>
       </c>
       <c r="I65" t="n">
         <v>1792.721820288865</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K65" t="n">
-        <v>7.49</v>
+        <v>6.26</v>
       </c>
       <c r="L65" t="n">
         <v>1.55</v>
@@ -4146,7 +4925,7 @@
         <v>1.03</v>
       </c>
       <c r="N65" t="n">
-        <v>1.36</v>
+        <v>2.03</v>
       </c>
       <c r="O65" t="n">
         <v>-1.54</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,14 @@
       <c r="Q66" t="n">
         <v>32</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6308,7 +7107,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -6318,7 +7117,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6328,7 +7127,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>123.2</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
@@ -6338,7 +7137,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6348,7 +7147,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="10">
@@ -6358,7 +7157,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55.4</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="11">
@@ -6398,7 +7197,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.17</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="15">
@@ -6408,7 +7207,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.85</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="16">
@@ -6418,7 +7217,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.5</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="17">
@@ -6428,7 +7227,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13.19</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="18">
@@ -6438,7 +7237,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.9</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="19">
@@ -6448,7 +7247,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.01</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="20">
@@ -6458,7 +7257,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="21">
@@ -6468,7 +7267,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.98</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="22">
@@ -6478,7 +7277,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -6488,7 +7287,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -6498,7 +7297,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="25">
@@ -6518,7 +7317,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="27">
@@ -6528,7 +7327,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.31</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="28">
@@ -6538,7 +7337,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
